--- a/data/pack/eu/leche.xlsx
+++ b/data/pack/eu/leche.xlsx
@@ -14816,7 +14816,7 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>45.53</v>
+        <v>46.02</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
